--- a/Result/profitability/2906.xlsx
+++ b/Result/profitability/2906.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13625</v>
+        <v>0.18375</v>
       </c>
       <c r="N2" t="n">
-        <v>28.42</v>
+        <v>28.7325</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09124999999999998</v>
+        <v>0.1075</v>
       </c>
       <c r="N3" t="n">
-        <v>27.76</v>
+        <v>28.06</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07375</v>
+        <v>0.115</v>
       </c>
       <c r="N4" t="n">
-        <v>26.74875</v>
+        <v>27.18625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0825</v>
+        <v>0.13</v>
       </c>
       <c r="N5" t="n">
-        <v>26.46875</v>
+        <v>26.6325</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09625</v>
+        <v>0.1525</v>
       </c>
       <c r="N6" t="n">
-        <v>25.32</v>
+        <v>25.68</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09625</v>
+        <v>0.1025</v>
       </c>
       <c r="N7" t="n">
-        <v>25.085</v>
+        <v>25.2125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0675</v>
+        <v>0.11125</v>
       </c>
       <c r="N8" t="n">
-        <v>23.86</v>
+        <v>24.10375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E75" t="n">
+        <v>639</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>42</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>136</v>
+      </c>
+      <c r="J75" t="n">
+        <v>179</v>
+      </c>
+      <c r="K75" t="n">
+        <v>88</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.695</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.949999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06567867969013141</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.310000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04319155951203446</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
